--- a/ALL_NBA_PLAYERS_with_headshots.xlsx
+++ b/ALL_NBA_PLAYERS_with_headshots.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F473"/>
+  <dimension ref="A1:F471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>Missouri Valley Conference</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>Missouri Valley Conference</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>Missouri Valley Conference</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>The American</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mountain East Conference</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>Missouri Valley Conference</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -7423,912 +7423,912 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Jonas Valančiūnas</t>
+          <t>Jonathan Isaac</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Lietuvos rytas Vilnius</t>
+          <t>Florida State</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>202685</v>
+        <v>1628371</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202685.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628371.png</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>202685.png</t>
+          <t>1628371.png</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Jonathan Isaac</t>
+          <t>Jonathan Mogbo</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Florida State</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1628371</v>
+        <v>1642367</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628371.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642367.png</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>1628371.png</t>
+          <t>1642367.png</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Jonathan Mogbo</t>
+          <t>Jordan Clarkson</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1642367</v>
+        <v>203903</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642367.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203903.png</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>1642367.png</t>
+          <t>203903.png</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Jordan Clarkson</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>203903</v>
+        <v>1630692</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203903.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630692.png</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>203903.png</t>
+          <t>1630692.png</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1630692</v>
+        <v>1641722</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630692.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641722.png</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>1630692.png</t>
+          <t>1641722.png</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>Jordan McLaughlin</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1641722</v>
+        <v>1629162</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641722.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629162.png</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>1641722.png</t>
+          <t>1629162.png</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Jordan McLaughlin</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1629162</v>
+        <v>1641757</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629162.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641757.png</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>1629162.png</t>
+          <t>1641757.png</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1641757</v>
+        <v>1629673</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641757.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629673.png</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>1641757.png</t>
+          <t>1629673.png</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Jordan Walsh</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1629673</v>
+        <v>1641775</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629673.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641775.png</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>1629673.png</t>
+          <t>1641775.png</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Jordan Walsh</t>
+          <t>Jose Alvarado</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1641775</v>
+        <v>1630631</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641775.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630631.png</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>1641775.png</t>
+          <t>1630631.png</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Jose Alvarado</t>
+          <t>Josh Green</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1630631</v>
+        <v>1630182</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630631.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630182.png</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>1630631.png</t>
+          <t>1630182.png</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Josh Green</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1630182</v>
+        <v>1628404</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630182.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628404.png</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>1630182.png</t>
+          <t>josh_hart.png</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Josh Minott</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1628404</v>
+        <v>1631169</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628404.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631169.png</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>josh_hart.png</t>
+          <t>1631169.png</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Josh Minott</t>
+          <t>Josh Oduro</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1631169</v>
+        <v>1642490</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631169.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642490.png</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>1631169.png</t>
+          <t>1642490.png</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Josh Oduro</t>
+          <t>Josh Okogie</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1642490</v>
+        <v>1629006</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642490.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629006.png</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1642490.png</t>
+          <t>1629006.png</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Josh Okogie</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1629006</v>
+        <v>201950</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629006.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201950.png</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>1629006.png</t>
+          <t>201950.png</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>201950</v>
+        <v>1630577</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201950.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630577.png</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>201950.png</t>
+          <t>1630577.png</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Julian Phillips</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1630577</v>
+        <v>1641763</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630577.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641763.png</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>1630577.png</t>
+          <t>1641763.png</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Julian Phillips</t>
+          <t>Julian Reese</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1641763</v>
+        <v>1642882</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641763.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642882.png</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>1641763.png</t>
+          <t>1642882.png</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Julian Reese</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1642882</v>
+        <v>1631124</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642882.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631124.png</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>1642882.png</t>
+          <t>1631124.png</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1631124</v>
+        <v>203944</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631124.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203944.png</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>1631124.png</t>
+          <t>julius_randle.png</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Justin Champagnie</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>203944</v>
+        <v>1630551</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203944.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630551.png</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>julius_randle.png</t>
+          <t>1630551.png</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Justin Champagnie</t>
+          <t>Justin Edwards</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1630551</v>
+        <v>1642348</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630551.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642348.png</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>1630551.png</t>
+          <t>1642348.png</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Justin Edwards</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1642348</v>
+        <v>1642354</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642348.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642354.png</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>1642348.png</t>
+          <t>1642354.png</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1642354</v>
+        <v>1642880</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642354.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642880.png</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>1642354.png</t>
+          <t>1642880.png</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1642880</v>
+        <v>1626157</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642880.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626157.png</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>1642880.png</t>
+          <t>karl_anthony_towns.png</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Kasparas Jakučionis</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1626157</v>
+        <v>1642857</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626157.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642857.png</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>karl_anthony_towns.png</t>
+          <t>1642857.png</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Kasparas Jakučionis</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>San Diego State</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Mountain West</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1642857</v>
+        <v>202695</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642857.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202695.png</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>1642857.png</t>
+          <t>kawhi_leonard.png</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Keaton Wallace</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>San Diego State</t>
+          <t>UTSA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Mountain West</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>202695</v>
+        <v>1630811</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202695.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630811.png</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>kawhi_leonard.png</t>
+          <t>1630811.png</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Keaton Wallace</t>
+          <t>Keegan Murray</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>UTSA</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>American Athletic Conference</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1630811</v>
+        <v>1631099</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630811.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631099.png</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>1630811.png</t>
+          <t>1631099.png</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Keegan Murray</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8337,208 +8337,208 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1631099</v>
+        <v>1642276</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631099.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642276.png</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>1631099.png</t>
+          <t>1642276.png</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1642276</v>
+        <v>1629640</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642276.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629640.png</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>1642276.png</t>
+          <t>1629640.png</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Kelly Olynyk</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1629640</v>
+        <v>203482</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629640.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203482.png</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>1629640.png</t>
+          <t>203482.png</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Kelly Olynyk</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>203482</v>
+        <v>1626162</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203482.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626162.png</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>203482.png</t>
+          <t>1626162.png</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Kennedy Chandler</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1626162</v>
+        <v>1631113</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626162.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631113.png</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>1626162.png</t>
+          <t>1631113.png</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Kennedy Chandler</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1631113</v>
+        <v>1629026</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631113.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629026.png</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>1631113.png</t>
+          <t>1629026.png</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Kentavious Caldwell-Pope</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1629026</v>
+        <v>203484</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629026.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203484.png</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>1629026.png</t>
+          <t>203484.png</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Kentavious Caldwell-Pope</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8547,58 +8547,58 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>203484</v>
+        <v>1631165</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203484.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631165.png</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>203484.png</t>
+          <t>1631165.png</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Keon Ellis</t>
+          <t>Keshad Johnson</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1631165</v>
+        <v>1642352</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631165.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642352.png</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>1631165.png</t>
+          <t>1642352.png</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Keshad Johnson</t>
+          <t>Keshon Gilbert</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Iowa State</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8607,88 +8607,88 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1642352</v>
+        <v>1642933</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642352.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642933.png</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>1642352.png</t>
+          <t>1642933.png</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Keshon Gilbert</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Iowa State</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1642933</v>
+        <v>201142</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642933.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201142.png</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>1642933.png</t>
+          <t>kevin_durant.png</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>201142</v>
+        <v>1628989</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201142.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628989.png</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>kevin_durant.png</t>
+          <t>1628989.png</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Kevin Love</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8697,88 +8697,88 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1628989</v>
+        <v>201567</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628989.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201567.png</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>1628989.png</t>
+          <t>201567.png</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Kevin Love</t>
+          <t>Kevin McCullar Jr.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>201567</v>
+        <v>1641755</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201567.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641755.png</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>201567.png</t>
+          <t>1641755.png</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Kevin McCullar Jr.</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1641755</v>
+        <v>1629645</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641755.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629645.png</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>1641755.png</t>
+          <t>1629645.png</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Kevon Looney</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8787,358 +8787,358 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1629645</v>
+        <v>1626172</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629645.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626172.png</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>1629645.png</t>
+          <t>1626172.png</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Kevon Looney</t>
+          <t>Keyonte George</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1626172</v>
+        <v>1641718</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626172.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641718.png</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>1626172.png</t>
+          <t>keyonte_george.png</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Keyonte George</t>
+          <t>Khaman Maluach</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1641718</v>
+        <v>1642863</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641718.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642863.png</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>keyonte_george.png</t>
+          <t>1642863.png</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Khaman Maluach</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1642863</v>
+        <v>203114</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642863.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203114.png</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>1642863.png</t>
+          <t>203114.png</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Washington State</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Pac-12</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>203114</v>
+        <v>202691</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203114.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202691.png</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>203114.png</t>
+          <t>klay_thompson.png</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Washington State</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Pac-12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>202691</v>
+        <v>1641738</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202691.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641738.png</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>klay_thompson.png</t>
+          <t>1641738.png</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Kobe Bufkin</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1641738</v>
+        <v>1641723</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641738.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641723.png</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>1641738.png</t>
+          <t>1641723.png</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Kobe Bufkin</t>
+          <t>Kobe Sanders</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Mountain West</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1641723</v>
+        <v>1642920</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641723.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642920.png</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>1641723.png</t>
+          <t>1642920.png</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Kobe Sanders</t>
+          <t>Koby Brea</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Mountain West</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1642920</v>
+        <v>1642886</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642920.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642886.png</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>1642920.png</t>
+          <t>1642886.png</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Koby Brea</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1642886</v>
+        <v>1642851</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642886.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642851.png</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>1642886.png</t>
+          <t>kon_knueppel.png</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1642851</v>
+        <v>1627739</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642851.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1627739.png</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>kon_knueppel.png</t>
+          <t>1627739.png</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1627739</v>
+        <v>1631200</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1627739.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631200.png</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>1627739.png</t>
+          <t>1631200.png</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Kyle Anderson</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9147,148 +9147,148 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1631200</v>
+        <v>203937</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631200.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203937.png</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>1631200.png</t>
+          <t>203937.png</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Kyle Anderson</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>203937</v>
+        <v>1642271</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203937.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642271.png</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>203937.png</t>
+          <t>1642271.png</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1642271</v>
+        <v>1628398</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642271.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628398.png</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>1642271.png</t>
+          <t>kyle_kuzma.png</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Kyle Lowry</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1628398</v>
+        <v>200768</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628398.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/200768.png</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>kyle_kuzma.png</t>
+          <t>200768.png</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Kyle Lowry</t>
+          <t>Kyrie Irving</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>200768</v>
+        <v>202681</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/200768.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202681.png</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>200768.png</t>
+          <t>202681.png</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Kyrie Irving</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9297,538 +9297,538 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>202681</v>
+        <v>1642273</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202681.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642273.png</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>202681.png</t>
+          <t>1642273.png</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Kyshawn George</t>
+          <t>LJ Cryer</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1642273</v>
+        <v>1643018</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642273.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1643018.png</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>1642273.png</t>
+          <t>1643018.png</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>LJ Cryer</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Wichita State</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1643018</v>
+        <v>1629013</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1643018.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629013.png</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>1643018.png</t>
+          <t>1629013.png</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Larry Nance Jr.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Wichita State</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Mountain West</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1629013</v>
+        <v>1626204</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629013.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626204.png</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>1629013.png</t>
+          <t>1626204.png</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Larry Nance Jr.</t>
+          <t>Lauri Markkanen</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain West</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1626204</v>
+        <v>1628374</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626204.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628374.png</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>1626204.png</t>
+          <t>1628374.png</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Lauri Markkanen</t>
+          <t>Leaky Black</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1628374</v>
+        <v>1641778</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628374.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641778.png</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>1628374.png</t>
+          <t>1641778.png</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Leaky Black</t>
+          <t>Liam McNeeley</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1641778</v>
+        <v>1642862</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641778.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642862.png</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>1641778.png</t>
+          <t>1642862.png</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Liam McNeeley</t>
+          <t>Lindy Waters III</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Oklahoma State</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1642862</v>
+        <v>1630322</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642862.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630322.png</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>1642862.png</t>
+          <t>1630322.png</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Lindy Waters III</t>
+          <t>Lucas Williamson</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Oklahoma State</t>
+          <t>Loyola-Chicago</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1630322</v>
+        <v>1631351</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630322.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631351.png</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>1630322.png</t>
+          <t>1631351.png</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lucas Williamson</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Loyola-Chicago</t>
+          <t>Arizona State</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1631351</v>
+        <v>1629652</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631351.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629652.png</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>1631351.png</t>
+          <t>1629652.png</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Luka Garza</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Arizona State</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1629652</v>
+        <v>1630568</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629652.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630568.png</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>1629652.png</t>
+          <t>1630568.png</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Luka Garza</t>
+          <t>Luke Kennard</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1630568</v>
+        <v>1628379</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630568.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628379.png</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>1630568.png</t>
+          <t>1628379.png</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Luke Kennard</t>
+          <t>Luke Kornet</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1628379</v>
+        <v>1628436</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628379.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628436.png</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>1628379.png</t>
+          <t>1628436.png</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Luke Kornet</t>
+          <t>Mac McClung</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1628436</v>
+        <v>1630644</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628436.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630644.png</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>1628436.png</t>
+          <t>1630644.png</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Mac McClung</t>
+          <t>Malachi Smith</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1630644</v>
+        <v>1641869</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630644.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641869.png</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>1630644.png</t>
+          <t>1641869.png</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Malachi Smith</t>
+          <t>Malevy Leons</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Bradley</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>Missouri Valley Conference</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1641869</v>
+        <v>1642502</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641869.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642502.png</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1641869.png</t>
+          <t>1642502.png</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Malevy Leons</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1642502</v>
+        <v>1628370</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642502.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628370.png</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1642502.png</t>
+          <t>1628370.png</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Marcus Sasser</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1628370</v>
+        <v>1631204</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628370.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631204.png</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>1628370.png</t>
+          <t>1631204.png</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Marcus Sasser</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Oklahoma State</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9837,113 +9837,113 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1631204</v>
+        <v>203935</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631204.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203935.png</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>1631204.png</t>
+          <t>203935.png</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Oklahoma State</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>203935</v>
+        <v>1631109</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203935.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631109.png</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>203935.png</t>
+          <t>1631109.png</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Mark Williams</t>
+          <t>Markelle Fultz</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1631109</v>
+        <v>1628365</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631109.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628365.png</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1631109.png</t>
+          <t>1628365.png</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Markelle Fultz</t>
+          <t>Marvin Bagley III</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1628365</v>
+        <v>1628963</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628365.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628963.png</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>1628365.png</t>
+          <t>1628963.png</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Marvin Bagley III</t>
+          <t>Mason Plumlee</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9957,58 +9957,58 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1628963</v>
+        <v>203486</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628963.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203486.png</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>1628963.png</t>
+          <t>203486.png</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Mason Plumlee</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>203486</v>
+        <v>1629680</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203486.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629680.png</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>203486.png</t>
+          <t>1629680.png</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10017,268 +10017,268 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1629680</v>
+        <v>1631108</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629680.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631108.png</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>1629680.png</t>
+          <t>1631108.png</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Max Shulga</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1631108</v>
+        <v>1642917</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631108.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642917.png</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1631108.png</t>
+          <t>1642917.png</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Max Shulga</t>
+          <t>Max Strus</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1642917</v>
+        <v>1629622</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642917.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629622.png</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>1642917.png</t>
+          <t>1629622.png</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1629622</v>
+        <v>1642875</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629622.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642875.png</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>1629622.png</t>
+          <t>1642875.png</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1642875</v>
+        <v>1642877</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642875.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642877.png</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>1642875.png</t>
+          <t>1642877.png</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Micah Peavy</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1642877</v>
+        <v>1630695</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642877.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630695.png</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>1642877.png</t>
+          <t>1630695.png</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1630695</v>
+        <v>1629008</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630695.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629008.png</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>1630695.png</t>
+          <t>1629008.png</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1629008</v>
+        <v>1628969</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629008.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628969.png</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>1629008.png</t>
+          <t>mikal_bridges.png</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Ohio State</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1628969</v>
+        <v>201144</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628969.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201144.png</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>mikal_bridges.png</t>
+          <t>201144.png</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Ohio State</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10287,478 +10287,478 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>201144</v>
+        <v>1628970</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201144.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628970.png</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>201144.png</t>
+          <t>miles_bridges.png</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1628970</v>
+        <v>1630540</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628970.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630540.png</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>miles_bridges.png</t>
+          <t>1630540.png</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Western Kentucky</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Conference USA</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1630540</v>
+        <v>1629011</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630540.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629011.png</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>1630540.png</t>
+          <t>1629011.png</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Moritz Wagner</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Western Kentucky</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Conference USA</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1629011</v>
+        <v>1629021</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629011.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629021.png</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>1629011.png</t>
+          <t>1629021.png</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Moritz Wagner</t>
+          <t>Moses Moody</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1629021</v>
+        <v>1630541</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629021.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630541.png</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>1629021.png</t>
+          <t>1630541.png</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Moses Moody</t>
+          <t>Mouhamed Gueye</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Washington State</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Pac-12</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1630541</v>
+        <v>1631243</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630541.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631243.png</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>1630541.png</t>
+          <t>1631243.png</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mouhamed Gueye</t>
+          <t>Moussa Cisse</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Washington State</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Pac-12</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1631243</v>
+        <v>1630619</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631243.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630619.png</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>1631243.png</t>
+          <t>1630619.png</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Moussa Cisse</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1630619</v>
+        <v>1631217</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630619.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631217.png</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>1630619.png</t>
+          <t>1631217.png</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1631217</v>
+        <v>1626167</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631217.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626167.png</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>1631217.png</t>
+          <t>myles_turner.png</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Myron Gardner</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Arkansas-Little Rock</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Ohio Valley</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1626167</v>
+        <v>1642066</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626167.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642066.png</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>myles_turner.png</t>
+          <t>1642066.png</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Myron Gardner</t>
+          <t>Nae'Qwan Tomlin</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Arkansas-Little Rock</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Ohio Valley</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1642066</v>
+        <v>1641772</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642066.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641772.png</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>1642066.png</t>
+          <t>1641772.png</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Nae'Qwan Tomlin</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1641772</v>
+        <v>1630230</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641772.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630230.png</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>1641772.png</t>
+          <t>1630230.png</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Nate Williams</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Mid-American</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1630230</v>
+        <v>1631466</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630230.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631466.png</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>1630230.png</t>
+          <t>1631466.png</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Nate Williams</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mid-American</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1631466</v>
+        <v>1629675</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631466.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629675.png</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>1631466.png</t>
+          <t>1629675.png</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Utah State</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Pac-12</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1629675</v>
+        <v>1629674</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629675.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629674.png</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>1629675.png</t>
+          <t>1629674.png</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Utah State</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Pac-12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1629674</v>
+        <v>1629651</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629674.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629651.png</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>1629674.png</t>
+          <t>nic_claxton.png</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Nick Richards</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10767,28 +10767,28 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1629651</v>
+        <v>1630208</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629651.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630208.png</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>nic_claxton.png</t>
+          <t>1630208.png</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Nick Richards</t>
+          <t>Nick Smith Jr.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10797,473 +10797,473 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1630208</v>
+        <v>1641733</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630208.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641733.png</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>1630208.png</t>
+          <t>1641733.png</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Nick Smith Jr.</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1641733</v>
+        <v>1629638</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641733.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629638.png</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>1641733.png</t>
+          <t>1629638.png</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Nikola Vučević</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1629638</v>
+        <v>202696</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629638.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202696.png</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>1629638.png</t>
+          <t>202696.png</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Nicolas Batum</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Colorado State</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mountain West</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>201587</v>
+        <v>1642363</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201587.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642363.png</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>201587.png</t>
+          <t>1642363.png</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Nikola Vučević</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>202696</v>
+        <v>1641730</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202696.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641730.png</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>202696.png</t>
+          <t>1641730.png</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Norchad Omier</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Colorado State</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mountain West</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1642363</v>
+        <v>1641807</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642363.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641807.png</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>1642363.png</t>
+          <t>1641807.png</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1641730</v>
+        <v>1626181</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641730.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626181.png</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>1641730.png</t>
+          <t>norman_powell.png</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Norchad Omier</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1641807</v>
+        <v>1628384</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641807.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628384.png</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>1641807.png</t>
+          <t>og_anunoby.png</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Dayton</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1626181</v>
+        <v>1630167</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626181.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630167.png</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>norman_powell.png</t>
+          <t>1630167.png</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1628384</v>
+        <v>1630534</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628384.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630534.png</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>og_anunoby.png</t>
+          <t>1630534.png</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Olivier Sarr</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Dayton</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1630167</v>
+        <v>1630846</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630167.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630846.png</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>1630167.png</t>
+          <t>1630846.png</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1630534</v>
+        <v>1641765</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630534.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641765.png</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>1630534.png</t>
+          <t>1641765.png</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Olivier Sarr</t>
+          <t>Omer Yurtseven</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1630846</v>
+        <v>1630209</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630846.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630209.png</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>1630846.png</t>
+          <t>1630209.png</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1641765</v>
+        <v>1630168</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641765.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630168.png</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>1641765.png</t>
+          <t>1630168.png</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Omer Yurtseven</t>
+          <t>Oscar Tshiebwe</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1630209</v>
+        <v>1631131</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630209.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631131.png</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>1630209.png</t>
+          <t>1631131.png</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1630168</v>
+        <v>1642345</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630168.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642345.png</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>1630168.png</t>
+          <t>1642345.png</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Oscar Tshiebwe</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11277,118 +11277,118 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1631131</v>
+        <v>1629023</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631131.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629023.png</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>1631131.png</t>
+          <t>1629023.png</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>PJ Hall</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1642345</v>
+        <v>1641790</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642345.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641790.png</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>1642345.png</t>
+          <t>1641790.png</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1629023</v>
+        <v>1631094</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629023.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631094.png</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>1629023.png</t>
+          <t>paolo_banchero.png</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>PJ Hall</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Conference USA</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1641790</v>
+        <v>1627783</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641790.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1627783.png</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>1641790.png</t>
+          <t>pascal_siakam.png</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Pat Connaughton</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Notre Dame</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11397,268 +11397,268 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1631094</v>
+        <v>1626192</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631094.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626192.png</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>paolo_banchero.png</t>
+          <t>1626192.png</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>New Mexico State</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>C-USA</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1627783</v>
+        <v>1630311</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1627783.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630311.png</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>pascal_siakam.png</t>
+          <t>1630311.png</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Pat Connaughton</t>
+          <t>Patrick Baldwin Jr.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Notre Dame</t>
+          <t>Wisconsin-Milwaukee</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Horizon League</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1626192</v>
+        <v>1631116</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626192.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631116.png</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>1626192.png</t>
+          <t>1631116.png</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Patrick Williams</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Florida State</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1630311</v>
+        <v>1630172</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630311.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630172.png</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>1630311.png</t>
+          <t>1630172.png</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Patrick Baldwin Jr.</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Wisconsin-Milwaukee</t>
+          <t>Fresno State</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Horizon League</t>
+          <t>Mountain West</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1631116</v>
+        <v>202331</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631116.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202331.png</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>1631116.png</t>
+          <t>202331.png</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Patrick Williams</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Florida State</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1630172</v>
+        <v>1630194</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630172.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630194.png</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>1630172.png</t>
+          <t>1630194.png</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Fresno State</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mountain West</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>202331</v>
+        <v>1630202</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202331.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630202.png</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>202331.png</t>
+          <t>payton_pritchard.png</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Payton Sandfort</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1630194</v>
+        <v>1642362</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630194.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642362.png</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>1630194.png</t>
+          <t>1642362.png</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1630202</v>
+        <v>1641796</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630202.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641796.png</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>payton_pritchard.png</t>
+          <t>1641796.png</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Payton Sandfort</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11667,323 +11667,323 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1642362</v>
+        <v>1631250</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642362.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631250.png</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>1642362.png</t>
+          <t>1631250.png</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1641796</v>
+        <v>1631212</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641796.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631212.png</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>1641796.png</t>
+          <t>1631212.png</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1631250</v>
+        <v>1630173</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631250.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630173.png</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>1631250.png</t>
+          <t>1630173.png</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1631212</v>
+        <v>1629656</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631212.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629656.png</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>1631212.png</t>
+          <t>1629656.png</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1630173</v>
+        <v>1631245</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630173.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631245.png</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>1630173.png</t>
+          <t>1631245.png</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Quinten Post</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1629656</v>
+        <v>1642366</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629656.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642366.png</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>1629656.png</t>
+          <t>1642366.png</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1631245</v>
+        <v>1629628</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631245.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629628.png</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>1631245.png</t>
+          <t>rj_barrett.png</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Quinten Post</t>
+          <t>Rasheer Fleming</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>St. Joseph's (PA)</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1642366</v>
+        <v>1642853</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642366.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642853.png</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>1642366.png</t>
+          <t>1642853.png</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>RayJ Dennis</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1629628</v>
+        <v>1642484</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629628.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642484.png</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>rj_barrett.png</t>
+          <t>1642484.png</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Rasheer Fleming</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>St. Joseph's (PA)</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1642853</v>
+        <v>1642263</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642853.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642263.png</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>1642853.png</t>
+          <t>1642263.png</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>RayJ Dennis</t>
+          <t>Riley Minix</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Morehead State</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Ohio Valley</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1642484</v>
+        <v>1642434</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642484.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642434.png</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>1642484.png</t>
+          <t>1642434.png</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11997,568 +11997,568 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1642263</v>
+        <v>1642265</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642263.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642265.png</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>1642263.png</t>
+          <t>1642265.png</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Riley Minix</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Morehead State</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Ohio Valley</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1642434</v>
+        <v>1629057</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642434.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629057.png</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>1642434.png</t>
+          <t>1629057.png</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Ron Harper Jr.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Rutgers</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1642265</v>
+        <v>1631199</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642265.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631199.png</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>1642265.png</t>
+          <t>1631199.png</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1629057</v>
+        <v>1626220</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629057.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626220.png</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>1629057.png</t>
+          <t>1626220.png</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ron Harper Jr.</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Rutgers</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1631199</v>
+        <v>1629060</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631199.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629060.png</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>1631199.png</t>
+          <t>rui_hachimura.png</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Russell Westbrook</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1626220</v>
+        <v>201566</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626220.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201566.png</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>1626220.png</t>
+          <t>201566.png</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Ryan Dunn</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1629060</v>
+        <v>1642346</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629060.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642346.png</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>rui_hachimura.png</t>
+          <t>1642346.png</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Russell Westbrook</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>201566</v>
+        <v>1641750</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201566.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641750.png</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>201566.png</t>
+          <t>1641750.png</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ryan Dunn</t>
+          <t>Ryan Nembhard</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1642346</v>
+        <v>1642948</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642346.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642948.png</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>1642346.png</t>
+          <t>1642948.png</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Mid-American</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1641750</v>
+        <v>1631157</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641750.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631157.png</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1641750.png</t>
+          <t>1631157.png</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Ryan Nembhard</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1642948</v>
+        <v>1630180</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642948.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630180.png</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>1642948.png</t>
+          <t>1630180.png</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mid-American</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1631157</v>
+        <v>1630573</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631157.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630573.png</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>1631157.png</t>
+          <t>sam_hauser.png</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Utah State</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Pac-12</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1630180</v>
+        <v>1630241</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630180.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630241.png</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>1630180.png</t>
+          <t>1630241.png</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Seton Hall</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1630573</v>
+        <v>1630572</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630573.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630572.png</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>sam_hauser.png</t>
+          <t>1630572.png</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Utah State</t>
+          <t>Loyola-Maryland</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Pac-12</t>
+          <t>Patriot League</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1630241</v>
+        <v>1630583</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630241.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630583.png</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>1630241.png</t>
+          <t>1630583.png</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Seton Hall</t>
+          <t>Florida State</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1630572</v>
+        <v>1630567</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630572.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630567.png</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>1630572.png</t>
+          <t>scottie_barnes.png</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Scotty Pippen Jr.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Loyola-Maryland</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Patriot League</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1630583</v>
+        <v>1630590</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630583.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630590.png</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>1630583.png</t>
+          <t>1630590.png</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Sean Pedulla</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Florida State</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1630567</v>
+        <v>1642951</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630567.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642951.png</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>scottie_barnes.png</t>
+          <t>1642951.png</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Scotty Pippen Jr.</t>
+          <t>Seth Curry</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1630590</v>
+        <v>203552</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630590.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203552.png</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>1630590.png</t>
+          <t>203552.png</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Sean Pedulla</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12567,58 +12567,58 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>1642951</v>
+        <v>1631101</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642951.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631101.png</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>1642951.png</t>
+          <t>1631101.png</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Seth Curry</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>203552</v>
+        <v>1628983</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203552.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628983.png</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>203552.png</t>
+          <t>shai_gilgeous_alexander.png</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Sharife Cooper</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12627,448 +12627,448 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1631101</v>
+        <v>1630536</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631101.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630536.png</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>1631101.png</t>
+          <t>1630536.png</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1628983</v>
+        <v>1642883</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628983.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642883.png</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>shai_gilgeous_alexander.png</t>
+          <t>1642883.png</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Sharife Cooper</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1630536</v>
+        <v>1642461</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630536.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642461.png</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>1630536.png</t>
+          <t>1642461.png</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1642883</v>
+        <v>201939</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642883.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201939.png</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>1642883.png</t>
+          <t>201939.png</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1642461</v>
+        <v>1642264</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642461.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642264.png</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>1642461.png</t>
+          <t>stephon_castle.png</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Steven Adams</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>201939</v>
+        <v>203500</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201939.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203500.png</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>201939.png</t>
+          <t>203500.png</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Svi Mykhailiuk</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1642264</v>
+        <v>1629004</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642264.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629004.png</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>stephon_castle.png</t>
+          <t>1629004.png</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Steven Adams</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>203500</v>
+        <v>204456</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203500.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/204456.png</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>203500.png</t>
+          <t>204456.png</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Svi Mykhailiuk</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Conference USA</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1629004</v>
+        <v>1643007</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629004.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1643007.png</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>1629004.png</t>
+          <t>1643007.png</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Taj Gibson</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>204456</v>
+        <v>201959</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/204456.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201959.png</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>204456.png</t>
+          <t>201959.png</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Conference USA</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>1643007</v>
+        <v>1631106</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1643007.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631106.png</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>1643007.png</t>
+          <t>1631106.png</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Taj Gibson</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>201959</v>
+        <v>1627752</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/201959.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1627752.png</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>201959.png</t>
+          <t>1627752.png</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1631106</v>
+        <v>1641707</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631106.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641707.png</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>1631106.png</t>
+          <t>1641707.png</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Terance Mann</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Florida State</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1627752</v>
+        <v>1629611</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1627752.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629611.png</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>1627752.png</t>
+          <t>terance_mann.png</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Terrence Shannon Jr.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1641707</v>
+        <v>1630545</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641707.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630545.png</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>1641707.png</t>
+          <t>1630545.png</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Terry Rozier</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Florida State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -13077,28 +13077,28 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1629611</v>
+        <v>1626179</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629611.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626179.png</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>terance_mann.png</t>
+          <t>1626179.png</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Terrence Shannon Jr.</t>
+          <t>Thomas Bryant</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -13107,58 +13107,58 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>1630545</v>
+        <v>1628418</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630545.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628418.png</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>1630545.png</t>
+          <t>1628418.png</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Terry Rozier</t>
+          <t>Thomas Sorber</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1626179</v>
+        <v>1642850</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626179.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642850.png</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>1626179.png</t>
+          <t>1642850.png</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Thomas Bryant</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -13167,208 +13167,208 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1628418</v>
+        <v>203501</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628418.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203501.png</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>1628418.png</t>
+          <t>203501.png</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Thomas Sorber</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1642850</v>
+        <v>202699</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642850.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202699.png</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>1642850.png</t>
+          <t>tobias_harris.png</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Tolu Smith</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Mississippi State</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>203501</v>
+        <v>1642449</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203501.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642449.png</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>203501.png</t>
+          <t>1642449.png</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Tosan Evbuomwan</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Princeton</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Ivy League</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>202699</v>
+        <v>1641787</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/202699.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641787.png</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>tobias_harris.png</t>
+          <t>1641787.png</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Tolu Smith</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Mississippi State</t>
+          <t>Dayton</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1642449</v>
+        <v>1641739</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642449.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641739.png</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>1642449.png</t>
+          <t>toumani_camara.png</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Tosan Evbuomwan</t>
+          <t>Trae Young</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Princeton</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Ivy League</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1641787</v>
+        <v>1629027</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641787.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629027.png</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>1641787.png</t>
+          <t>trae_young.png</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Trayce Jackson-Davis</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Dayton</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1641739</v>
+        <v>1631218</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641739.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631218.png</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>toumani_camara.png</t>
+          <t>1631218.png</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Trae Young</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -13377,58 +13377,58 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1629027</v>
+        <v>1642848</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629027.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642848.png</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>trae_young.png</t>
+          <t>1642848.png</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Trayce Jackson-Davis</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1631218</v>
+        <v>1630200</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631218.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630200.png</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>1631218.png</t>
+          <t>1630200.png</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Tre Mann</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -13437,353 +13437,353 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1642848</v>
+        <v>1630544</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642848.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630544.png</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>1642848.png</t>
+          <t>1630544.png</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Trendon Watford</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1630200</v>
+        <v>1630570</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630200.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630570.png</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>1630200.png</t>
+          <t>1630570.png</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Tre Mann</t>
+          <t>Trevor Keels</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1630544</v>
+        <v>1631211</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630544.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631211.png</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>1630544.png</t>
+          <t>1631211.png</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Trendon Watford</t>
+          <t>Trey Alexander</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1630570</v>
+        <v>1641725</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630570.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641725.png</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>1630570.png</t>
+          <t>1641725.png</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Trevor Keels</t>
+          <t>Trey Jemison III</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Alabama-Birmingham</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1631211</v>
+        <v>1641998</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631211.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641998.png</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>1631211.png</t>
+          <t>1641998.png</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Trey Alexander</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1641725</v>
+        <v>1630530</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641725.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630530.png</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>1641725.png</t>
+          <t>trey_murphy_iii.png</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Trey Jemison III</t>
+          <t>Tristan Enaruna</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Alabama-Birmingham</t>
+          <t>Cleveland State</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>American Athletic Conference</t>
+          <t>Horizon League</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1641998</v>
+        <v>1642400</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641998.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642400.png</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>1641998.png</t>
+          <t>1642400.png</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1630530</v>
+        <v>1641783</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630530.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641783.png</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>trey_murphy_iii.png</t>
+          <t>1641783.png</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Tristan Enaruna</t>
+          <t>Tristen Newton</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Cleveland State</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Horizon League</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1642400</v>
+        <v>1641803</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642400.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641803.png</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>1642400.png</t>
+          <t>1641803.png</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Ty Jerome</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1641783</v>
+        <v>1629660</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641783.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629660.png</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>1641783.png</t>
+          <t>1629660.png</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Tristen Newton</t>
+          <t>TyTy Washington Jr.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>1641803</v>
+        <v>1631102</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641803.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631102.png</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>1641803.png</t>
+          <t>1631102.png</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Ty Jerome</t>
+          <t>Tyler Burton</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Atlantic 10</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1629660</v>
+        <v>1631174</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629660.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631174.png</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>1629660.png</t>
+          <t>1631174.png</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>TyTy Washington Jr.</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -13797,88 +13797,88 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>1631102</v>
+        <v>1629639</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631102.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629639.png</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>1631102.png</t>
+          <t>tyler_herro.png</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Tyler Burton</t>
+          <t>Tyler Kolek</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Atlantic 10</t>
+          <t>Big East</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1631174</v>
+        <v>1642278</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631174.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642278.png</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>1631174.png</t>
+          <t>1642278.png</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Tyrese Haliburton</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Iowa State</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1629639</v>
+        <v>1630169</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629639.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630169.png</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>tyler_herro.png</t>
+          <t>1630169.png</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Tyler Kolek</t>
+          <t>Tyrese Martin</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -13887,113 +13887,113 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1642278</v>
+        <v>1631213</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642278.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631213.png</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>1642278.png</t>
+          <t>1631213.png</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Tyrese Haliburton</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Iowa State</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1630169</v>
+        <v>1630178</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630169.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630178.png</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>1630169.png</t>
+          <t>1630178.png</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Tyrese Martin</t>
+          <t>Tyrese Proctor</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Big East</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>1631213</v>
+        <v>1642878</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631213.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642878.png</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>1631213.png</t>
+          <t>1642878.png</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Tyson Etienne</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Wichita State</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>American Athletic Conference</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1630178</v>
+        <v>1630623</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630178.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630623.png</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>1630178.png</t>
+          <t>1630623.png</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Tyrese Proctor</t>
+          <t>Tyus Jones</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -14007,298 +14007,298 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1642878</v>
+        <v>1626145</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642878.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626145.png</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>1642878.png</t>
+          <t>1626145.png</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Tyson Etienne</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Wichita State</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1630623</v>
+        <v>1642845</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630623.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642845.png</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>1630623.png</t>
+          <t>1642845.png</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Tyus Jones</t>
+          <t>Vladislav Goldin</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1626145</v>
+        <v>1642884</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1626145.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642884.png</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>1626145.png</t>
+          <t>1642884.png</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Walker Kessler</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1642845</v>
+        <v>1631117</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642845.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631117.png</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>1642845.png</t>
+          <t>1631117.png</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Vladislav Goldin</t>
+          <t>Walter Clayton Jr.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1642884</v>
+        <v>1642383</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642884.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642383.png</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>1642884.png</t>
+          <t>1642383.png</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Walker Kessler</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1631117</v>
+        <v>1628976</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631117.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628976.png</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>1631117.png</t>
+          <t>wendell_carter_jr.png</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Walter Clayton Jr.</t>
+          <t>Wendell Moore Jr.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1642383</v>
+        <v>1631111</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642383.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631111.png</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>1642383.png</t>
+          <t>1631111.png</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1628976</v>
+        <v>1642954</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628976.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642954.png</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>wendell_carter_jr.png</t>
+          <t>1642954.png</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Wendell Moore Jr.</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1631111</v>
+        <v>1642860</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1631111.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642860.png</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>1631111.png</t>
+          <t>1642860.png</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Xavier Tillman</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1642954</v>
+        <v>1630214</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642954.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630214.png</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>1642954.png</t>
+          <t>1630214.png</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Yanic Konan Niederhäuser</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Penn State</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -14307,314 +14307,254 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1642860</v>
+        <v>1642949</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642860.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642949.png</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>1642860.png</t>
+          <t>1642949.png</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Xavier Tillman</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1630214</v>
+        <v>1642274</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630214.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642274.png</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>1630214.png</t>
+          <t>1642274.png</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Yanic Konan Niederhäuser</t>
+          <t>Zach Collins</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Penn State</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>West Coast Conference</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1642949</v>
+        <v>1628380</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642949.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628380.png</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>1642949.png</t>
+          <t>1628380.png</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1642274</v>
+        <v>1641744</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642274.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641744.png</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>1642274.png</t>
+          <t>1641744.png</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Zach Collins</t>
+          <t>Zach LaVine</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>Big Ten</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1628380</v>
+        <v>203897</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1628380.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203897.png</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>1628380.png</t>
+          <t>203897.png</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Zach Edey</t>
+          <t>Zeke Nnaji</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>Big 12</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1641744</v>
+        <v>1630192</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1641744.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630192.png</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>1641744.png</t>
+          <t>1630192.png</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Zach LaVine</t>
+          <t>Ziaire Williams</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Big Ten</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>203897</v>
+        <v>1630533</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/203897.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630533.png</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>203897.png</t>
+          <t>1630533.png</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Zeke Nnaji</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Big 12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1630192</v>
+        <v>1629627</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630192.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629627.png</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>1630192.png</t>
+          <t>zion_williamson.png</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Ziaire Williams</t>
+          <t>Zyon Pullin</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1630533</v>
+        <v>1642389</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1630533.png</t>
+          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642389.png</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
-        <is>
-          <t>1630533.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Zion Williamson</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Duke</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D472" t="n">
-        <v>1629627</v>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1629627.png</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>zion_williamson.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>Zyon Pullin</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D473" t="n">
-        <v>1642389</v>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>https://cdn.nba.com/headshots/nba/latest/1040x760/1642389.png</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
         <is>
           <t>1642389.png</t>
         </is>
